--- a/data-rec/Август 2026.xlsx
+++ b/data-rec/Август 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\Отделы\Дирекция по организационному развитию и системе менеджмента качества\ОРСМК\Несоответствия\Инструкции и классификаторы\МОЕ\ИИ\Аналитика данных по качеству\Месяц рек\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8F9E0BD-E846-4E36-908E-FD8182F0E4C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EEF75E5-94C3-4623-A024-E16C609E59F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="22320" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="73">
   <si>
     <t>Регистрационный номер</t>
   </si>
@@ -345,11 +345,11 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -684,11 +684,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
       <c r="D1" s="2" t="s">
         <v>1</v>
       </c>
@@ -739,11 +739,11 @@
       </c>
     </row>
     <row r="2" spans="1:19" ht="70.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
       <c r="D2" s="3" t="s">
         <v>18</v>
       </c>
@@ -790,11 +790,11 @@
       <c r="S2" s="3"/>
     </row>
     <row r="3" spans="1:19" ht="70.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
       <c r="D3" s="3" t="s">
         <v>31</v>
       </c>
@@ -831,11 +831,11 @@
       <c r="S3" s="3"/>
     </row>
     <row r="4" spans="1:19" ht="106.05" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
       <c r="D4" s="3" t="s">
         <v>37</v>
       </c>
@@ -878,11 +878,11 @@
       <c r="S4" s="3"/>
     </row>
     <row r="5" spans="1:19" ht="10.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
       <c r="D5" s="3" t="s">
         <v>44</v>
       </c>
@@ -895,7 +895,9 @@
       <c r="G5" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="H5" s="3"/>
+      <c r="H5" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="I5" s="3" t="s">
         <v>47</v>
       </c>
@@ -913,11 +915,11 @@
       <c r="S5" s="3"/>
     </row>
     <row r="6" spans="1:19" ht="10.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
       <c r="D6" s="3" t="s">
         <v>44</v>
       </c>
@@ -930,7 +932,9 @@
       <c r="G6" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="H6" s="3"/>
+      <c r="H6" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="I6" s="3" t="s">
         <v>51</v>
       </c>
@@ -948,11 +952,11 @@
       <c r="S6" s="3"/>
     </row>
     <row r="7" spans="1:19" ht="58.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
       <c r="D7" s="3" t="s">
         <v>53</v>
       </c>
@@ -987,11 +991,11 @@
       <c r="S7" s="3"/>
     </row>
     <row r="8" spans="1:19" ht="118.05" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
       <c r="D8" s="3" t="s">
         <v>58</v>
       </c>
@@ -1026,11 +1030,11 @@
       <c r="S8" s="3"/>
     </row>
     <row r="9" spans="1:19" ht="58.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
       <c r="D9" s="3" t="s">
         <v>63</v>
       </c>
@@ -1068,15 +1072,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A3:C3"/>
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A9:C9"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A3:C3"/>
   </mergeCells>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.39370078740157483" bottom="0.39370078740157483" header="0" footer="0"/>
   <pageSetup paperSize="9" pageOrder="overThenDown" orientation="portrait"/>
